--- a/data/tongnan_2026_filled.xlsx
+++ b/data/tongnan_2026_filled.xlsx
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>24527</v>
+        <v>15000</v>
       </c>
       <c r="F16" s="10" t="n"/>
     </row>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7922377</v>
+        <v>2600000</v>
       </c>
       <c r="F22" s="10" t="n"/>
     </row>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2142000</v>
+        <v>700000</v>
       </c>
       <c r="F23" s="10" t="n"/>
     </row>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="F33" s="10" t="n"/>
     </row>
@@ -2678,7 +2678,7 @@
       <c r="D75" s="11" t="inlineStr"/>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>詹浩先答应做托管, 后续算居间费用; 城发集团子公司中标, HPWinner 以分包/采购方进入; 6月中旬挂网招标, 农历年底前完工</t>
+          <t>项目范围 15000 盏（城区共 24527 盏，本次升级范围）；詹浩先答应做托管, 后续算居间费用；城发集团子公司中标方向, HPWinner 以分包/采购方进入；6月中旬挂网招标, 农历年底前完工</t>
         </is>
       </c>
       <c r="F75" s="10" t="n"/>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>10456</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="78">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>18136</v>
+        <v>8609</v>
       </c>
     </row>
     <row r="80">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>8386165</v>
+        <v>2750000</v>
       </c>
     </row>
     <row r="82">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6617357</v>
+        <v>2170000</v>
       </c>
     </row>
     <row r="83">
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1506000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="84">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1367000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="85">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>一次节能 59% (功率降低), 二次调光节能 69% (含调光叠加)</t>
+          <t>一次节能 59%, 二次调光节能 69%（按项目范围 15000 盏 / 城区共 24527 盏）</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>24527</v>
+        <v>15000</v>
       </c>
       <c r="F16" s="10" t="n"/>
     </row>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7922377</v>
+        <v>2600000</v>
       </c>
       <c r="F22" s="10" t="n"/>
     </row>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2142000</v>
+        <v>700000</v>
       </c>
       <c r="F23" s="10" t="n"/>
     </row>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="F33" s="10" t="n"/>
     </row>
@@ -4845,7 +4845,7 @@
       <c r="D75" s="11" t="inlineStr"/>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>詹浩先答应做托管, 后续算居间费用; 城发集团子公司中标, HPWinner 以分包/采购方进入; 6月中旬挂网招标, 农历年底前完工</t>
+          <t>项目范围 15000 盏（城区共 24527 盏，本次升级范围）；詹浩先答应做托管, 后续算居间费用；城发集团子公司中标方向, HPWinner 以分包/采购方进入；6月中旬挂网招标, 农历年底前完工</t>
         </is>
       </c>
       <c r="F75" s="10" t="n"/>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>10456</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="78">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>18136</v>
+        <v>8609</v>
       </c>
     </row>
     <row r="80">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>8386165</v>
+        <v>2750000</v>
       </c>
     </row>
     <row r="82">
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6617357</v>
+        <v>2170000</v>
       </c>
     </row>
     <row r="83">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1506000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="84">
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1367000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="85">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>一次节能 59% (功率降低), 二次调光节能 69% (含调光叠加)</t>
+          <t>一次节能 59%, 二次调光节能 69%（按项目范围 15000 盏 / 城区共 24527 盏）</t>
         </is>
       </c>
     </row>

--- a/data/tongnan_2026_filled.xlsx
+++ b/data/tongnan_2026_filled.xlsx
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2600000</v>
+        <v>2250000</v>
       </c>
       <c r="F22" s="10" t="n"/>
     </row>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>700000</v>
+        <v>1050000</v>
       </c>
       <c r="F23" s="10" t="n"/>
     </row>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6396</v>
+        <v>10456</v>
       </c>
     </row>
     <row r="78">
@@ -2786,12 +2786,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B1a</t>
+          <t>B1c</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>上一年度电费支出</t>
+          <t>B1c 历史趋势：最早年度电费（全区/审计口径，如2023；与下方「本项目」B1 无关）</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2800,18 +2800,18 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2750000</v>
+        <v>6617357.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B1b</t>
+          <t>B1a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>前年度电费支出</t>
+          <t>上一年度电费支出</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2820,18 +2820,18 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2170000</v>
+        <v>7922377.24</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B2a</t>
+          <t>B1b</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>上一年度运维支出</t>
+          <t>前年度电费支出</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2840,18 +2840,18 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>500000</v>
+        <v>8386165.37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B2b</t>
+          <t>B2c</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>前年度运维支出</t>
+          <t>B2c 历史趋势：与上列电费同顺位的最早年度运维支出（含人工与维修等，与 B1c 同年）</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2860,40 +2860,38 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>450000</v>
+        <v>1506000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>B2a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>客户调研得出的节能率（如：一次X% 二次Y%）</t>
+          <t>上一年度运维支出</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>一次节能 59%, 二次调光节能 69%（按项目范围 15000 盏 / 城区共 24527 盏）</t>
-        </is>
+          <t>本币/年</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2142000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>B2b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>客户期望年度节省额（年节省目标）</t>
+          <t>前年度运维支出</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2902,26 +2900,68 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1000000</v>
+        <v>2142000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>客户调研得出的节能率（如：一次X% 二次Y%）</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>一次节能 59%, 二次调光节能 69%（按项目范围 15000 盏 / 城区共 24527 盏）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>客户期望年度节省额（年节省目标）</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>预期合同总金额（合同期合计）</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>本币</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="E89" t="n">
         <v>30000000</v>
       </c>
     </row>
@@ -3029,7 +3069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4953,32 +4993,29 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B1a</t>
+          <t>B1c</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Last year (Y-1) electricity bill</t>
+          <t>B1c Historic trend: oldest-year electricity (city/audit scope, e.g. 2023; not the project baseline B1 below)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>LC/yr</t>
         </is>
-      </c>
-      <c r="E81" t="n">
-        <v>2750000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B1b</t>
+          <t>B1a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Year before (Y-2) electricity bill</t>
+          <t>Last year (Y-1) electricity bill</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4987,18 +5024,18 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2170000</v>
+        <v>2750000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B2a</t>
+          <t>B1b</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Last year (Y-1) O&amp;M cost</t>
+          <t>Year before (Y-2) electricity bill</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5007,60 +5044,55 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>500000</v>
+        <v>2170000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B2b</t>
+          <t>B2c</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Year before (Y-2) O&amp;M cost</t>
+          <t>B2c Historic trend: O&amp;M for the same oldest year as B1c (aligned row)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>LC/yr</t>
         </is>
-      </c>
-      <c r="E84" t="n">
-        <v>450000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>B2a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Customer-surveyed savings rates (e.g. primary X% secondary Y%)</t>
+          <t>Last year (Y-1) O&amp;M cost</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>一次节能 59%, 二次调光节能 69%（按项目范围 15000 盏 / 城区共 24527 盏）</t>
-        </is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>B2b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Customer expected annual savings target</t>
+          <t>Year before (Y-2) O&amp;M cost</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5069,26 +5101,68 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1000000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Customer-surveyed savings rates (e.g. primary X% secondary Y%)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>一次节能 59%, 二次调光节能 69%（按项目范围 15000 盏 / 城区共 24527 盏）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Customer expected annual savings target</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Expected total contract value (over full term)</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Local currency</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="E89" t="n">
         <v>30000000</v>
       </c>
     </row>
@@ -6622,7 +6696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8525,12 +8599,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B1b</t>
+          <t>B1c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>annual_electricity_y_minus_2</t>
+          <t>annual_electricity_y_minus_3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8552,12 +8626,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B2a</t>
+          <t>B1b</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>annual_om_y_minus_1</t>
+          <t>annual_electricity_y_minus_2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8579,12 +8653,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B2b</t>
+          <t>B2a</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>annual_om_y_minus_2</t>
+          <t>annual_om_y_minus_1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8606,39 +8680,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>B2c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>surveyed_savings_rates_text</t>
+          <t>annual_om_y_minus_3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (trend)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>operating_profile</t>
+          <t>cost_baseline</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>B2b</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>expected_annual_savings</t>
+          <t>annual_om_y_minus_2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8648,37 +8722,91 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Yes (能源托管)</t>
+          <t>Yes (trend)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>financials</t>
+          <t>cost_baseline</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>surveyed_savings_rates_text</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>operating_profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>expected_annual_savings</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Yes (能源托管)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>contract_total_value</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Yes (能源托管)</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>contract</t>
         </is>
